--- a/macro/양식/키워드변경_양식.xlsx
+++ b/macro/양식/키워드변경_양식.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -486,11 +486,6 @@
           <t>비즈핏 키워드</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>유입플 키워드</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -511,11 +506,6 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>귀금속,귀금속방,귀금속위치</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>강남맛집,강남맛집추천</t>
         </is>
       </c>
     </row>
